--- a/scripts_data_misc/ARG_LAR_TempModeling_10-21-24.xlsx
+++ b/scripts_data_misc/ARG_LAR_TempModeling_10-21-24.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/avaisvil_usbr_gov/Documents/Documents/R/american_river_SDM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vanessa.Martinez\Desktop\ARG Modeling\September Modeling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1CA711D6-877D-4B08-9260-95B5FB82C13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ED225A1-7E48-4674-9866-716EC462910C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA711D6-877D-4B08-9260-95B5FB82C13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="10" xr2:uid="{D9870FF2-EA63-42E7-9ECC-F32F9C8AE035}"/>
+    <workbookView xWindow="52640" yWindow="410" windowWidth="22810" windowHeight="19480" activeTab="1" xr2:uid="{D9870FF2-EA63-42E7-9ECC-F32F9C8AE035}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario Summary" sheetId="11" r:id="rId1"/>
@@ -459,12 +459,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECEAD63D-6078-4EB2-A178-89B31B2A659C}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -475,7 +475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -486,7 +486,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -497,7 +497,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -508,7 +508,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -519,7 +519,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -530,7 +530,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -541,7 +541,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -552,7 +552,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -563,7 +563,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -574,7 +574,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -593,12 +593,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98958920-C020-4FDD-B416-09B53F6F70E0}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -632,7 +632,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -649,7 +649,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -666,7 +666,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -683,7 +683,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -700,7 +700,7 @@
         <v>17.57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -717,7 +717,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -751,7 +751,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -768,7 +768,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -785,7 +785,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -802,7 +802,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -819,7 +819,7 @@
         <v>16.46</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -836,7 +836,7 @@
         <v>16.38</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -853,7 +853,7 @@
         <v>16.39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -870,7 +870,7 @@
         <v>16.21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -887,7 +887,7 @@
         <v>16.14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -904,7 +904,7 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -921,7 +921,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -938,7 +938,7 @@
         <v>16.02</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -955,7 +955,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -972,7 +972,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -989,7 +989,7 @@
         <v>15.08</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>14.59</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>14.58</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>14.31</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>14.53</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>14.14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>13.54</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13.39</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>13.55</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13.55</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>13.39</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12.66</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12.54</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>12.42</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>12.45</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>12.35</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>12.18</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>12.02</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>11.88</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>12.06</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>11.68</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>11.64</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>11.43</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>11.26</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>11.18</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>11.05</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>11.04</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>10.89</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>10.69</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>10.41</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>10.02</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -1898,12 +1898,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C266FB-7DAD-4EAA-88D9-903262352143}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>17.57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>16.46</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>16.38</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>16.39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>16.21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>16.14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>16.02</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>15.03</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>14.66</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>14.06</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>14.11</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>13.89</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>14.31</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>14.56</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>14.39</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>14.61</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>14.21</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>13.61</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>13.45</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>13.63</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>13.44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>13.51</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>13.08</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>12.48</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>12.43</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>12.08</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>11.93</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>11.45</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>11.29</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>11.07</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>11.07</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>10.64</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>10.64</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>10.42</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>10.23</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>10.02</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -3203,12 +3203,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D21A8F-A07E-4905-A9B0-ECCB8EBCAB6E}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>17.96</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>17.940000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>17.54</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>17.010000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>16.98</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>16.34</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>15.68</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>15.41</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>15.72</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>15.66</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>15.32</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>15.37</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>15.02</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>15.08</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>14.78</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>14.26</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>14.28</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>14.69</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>14.69</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>14.57</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>14.06</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>13.85</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>13.59</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>13.61</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>13.48</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>13.32</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>13.29</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>12.63</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>12.54</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>12.48</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>12.23</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>12.07</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>11.88</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>11.76</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>11.48</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>11.49</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>11.28</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>11.27</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>10.79</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>10.42</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>10.31</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>10.07</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -4508,12 +4508,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199A4D8F-6A32-469A-9A33-30892449B515}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>17.09</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>17.43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>16.88</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>16.62</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>16.09</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>15.56</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>15.61</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>15.81</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>15.47</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>15.33</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>15.49</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>15.16</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>14.39</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>14.84</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>14.65</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>14.85</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>14.94</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>14.81</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>14.68</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>14.17</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>13.95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>13.67</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>13.59</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>13.44</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>13.04</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>12.76</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>12.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>12.37</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>12.21</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>11.99</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>11.71</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>11.58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>11.45</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>11.42</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>11.35</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>11.33</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>10.83</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>10.23</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>9.91</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -5813,12 +5813,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCC253-48E1-48D2-B490-5D8F58CA13B1}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>17.09</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>17.43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>16.88</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>16.62</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>16.09</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>15.56</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>15.55</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>15.52</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>15.14</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>15.03</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>15.09</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>14.95</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>14.89</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>14.71</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>14.94</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>14.86</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>14.21</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>13.99</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>13.71</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>13.73</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>13.63</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>13.49</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>13.16</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>13.11</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>12.69</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>12.68</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>12.43</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>12.26</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>12.04</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>11.74</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>11.49</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>11.56</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>11.44</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>11.34</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>10.84</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>10.91</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>10.46</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>10.11</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>10.01</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>9.91</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -7118,12 +7118,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9FE589-8C52-4710-AC22-58363DEB65A8}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>17.09</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -7191,7 +7191,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>17.43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>16.93</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>16.22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>15.71</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>15.46</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>15.86</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>15.86</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>15.54</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>15.41</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>15.58</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>15.55</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>15.23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>15.26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>14.97</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>14.45</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>14.46</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>14.74</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>14.96</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>14.74</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>14.23</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>14.01</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>13.72</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>13.65</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>13.51</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>13.49</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>13.18</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>13.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>12.83</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>12.45</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>12.28</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>12.06</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>11.92</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>11.76</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>11.63</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -8126,7 +8126,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>11.61</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>11.44</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>11.37</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>11.34</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>10.84</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>10.91</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>10.47</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>10.35</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>10.11</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>10.02</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>9.92</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -8423,12 +8423,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3982D326-C9ED-435F-9993-8B372EB6189C}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>17.09</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>17.43</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>16.93</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>16.22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>15.71</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>15.48</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>15.32</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>14.84</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>15.06</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>15.07</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>14.78</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>15.07</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>15.06</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>14.52</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>14.53</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>14.84</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>15.02</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>15.08</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>14.97</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>14.31</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>14.08</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>13.26</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>13.28</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>12.94</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>12.53</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>12.38</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>12.14</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>11.99</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>11.82</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>11.68</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>11.54</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>11.65</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>11.47</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>11.39</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>10.93</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>10.130000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>9.93</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -9728,12 +9728,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41F2A93-617F-460D-948E-DCA12945834D}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>18.149999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>18.23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>17.77</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>17.84</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>17.89</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>17.63</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>17.22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>17.32</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>17.18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>17.010000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>16.510000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>16.63</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>14.36</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>14.31</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>14.01</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>14.21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>14.24</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>14.28</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>14.13</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -10277,7 +10277,7 @@
         <v>14.34</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>13.96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>13.35</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>13.22</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>13.41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>13.39</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>13.28</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>13.37</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>12.48</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>12.16</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>11.73</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>11.93</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>11.56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>11.52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -10668,7 +10668,7 @@
         <v>11.33</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>11.16</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>11.09</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>10.98</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>10.96</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -10753,7 +10753,7 @@
         <v>10.82</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>10.58</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>10.64</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>10.59</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>9.86</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -10906,7 +10906,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -10991,7 +10991,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -11033,12 +11033,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8900B845-AD3D-4B3F-80A7-96005C3A7883}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -11140,7 +11140,7 @@
         <v>17.57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -11191,7 +11191,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -11208,7 +11208,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>16.55</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>16.420000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -11429,7 +11429,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -11446,7 +11446,7 @@
         <v>14.38</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>14.46</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>14.18</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>14.38</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -11565,7 +11565,7 @@
         <v>14.26</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>14.45</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -11599,7 +11599,7 @@
         <v>14.64</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>14.08</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>13.49</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>13.49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -11701,7 +11701,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>13.39</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>13.46</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -11786,7 +11786,7 @@
         <v>12.59</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>12.46</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>12.36</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -11837,7 +11837,7 @@
         <v>12.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -11854,7 +11854,7 @@
         <v>12.28</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>12.12</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -11888,7 +11888,7 @@
         <v>11.97</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -11905,7 +11905,7 @@
         <v>11.83</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>12.03</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>11.64</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -11990,7 +11990,7 @@
         <v>11.24</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>11.16</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>11.04</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>11.02</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>10.88</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>10.61</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>10.68</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>10.62</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -12126,7 +12126,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -12194,7 +12194,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>9.73</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
@@ -12338,12 +12338,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC6022E-1E16-48BF-834E-E1963C9881C2}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45583</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45584</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45585</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45586</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45587</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>17.57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45588</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45589</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45590</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45591</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>17.27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45592</v>
       </c>
@@ -12530,7 +12530,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45593</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45594</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45595</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45596</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45597</v>
       </c>
@@ -12615,7 +12615,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45598</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>16.55</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45599</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>16.420000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45600</v>
       </c>
@@ -12666,7 +12666,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45601</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45602</v>
       </c>
@@ -12700,7 +12700,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45603</v>
       </c>
@@ -12717,7 +12717,7 @@
         <v>15.31</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45604</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>14.92</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45605</v>
       </c>
@@ -12751,7 +12751,7 @@
         <v>14.11</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45606</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>14.23</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45607</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45608</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>13.97</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45609</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>14.18</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45610</v>
       </c>
@@ -12836,7 +12836,7 @@
         <v>14.21</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45611</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45612</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45613</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45614</v>
       </c>
@@ -12904,7 +12904,7 @@
         <v>14.71</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45615</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>14.12</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45616</v>
       </c>
@@ -12938,7 +12938,7 @@
         <v>13.51</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45617</v>
       </c>
@@ -12955,7 +12955,7 @@
         <v>13.37</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45618</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45619</v>
       </c>
@@ -12989,7 +12989,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45620</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>13.37</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45621</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>13.41</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45622</v>
       </c>
@@ -13040,7 +13040,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45623</v>
       </c>
@@ -13057,7 +13057,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45624</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>12.97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45625</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45626</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45627</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45628</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>12.43</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45629</v>
       </c>
@@ -13159,7 +13159,7 @@
         <v>12.33</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45630</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>12.16</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45631</v>
       </c>
@@ -13193,7 +13193,7 @@
         <v>12.01</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45632</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45633</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>12.05</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45634</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45635</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>11.63</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45636</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>11.42</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45637</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>11.26</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45638</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45639</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>11.05</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45640</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45641</v>
       </c>
@@ -13363,7 +13363,7 @@
         <v>10.88</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45642</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45643</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>10.69</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45644</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45645</v>
       </c>
@@ -13431,7 +13431,7 @@
         <v>10.41</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45646</v>
       </c>
@@ -13448,7 +13448,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45647</v>
       </c>
@@ -13465,7 +13465,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45648</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>10.01</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45649</v>
       </c>
@@ -13499,7 +13499,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -13516,7 +13516,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45651</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45652</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45653</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45654</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45655</v>
       </c>
@@ -13601,7 +13601,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45656</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45657</v>
       </c>
